--- a/data/GPS/Metricas_GPS13.xlsx
+++ b/data/GPS/Metricas_GPS13.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9C8BC-A0C3-46EA-A18A-DB9FEB01460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>eJy9lltv2jAUx7+KladVQhBCy+g0TWJDfVnLaKe26y6qjO0QF1+i2C4tiO8+27A2yYCVTM1Tck6Oz/n9j29ZBBhqooJ3YBFo6R/OYV+CKIy64XF4GDRAcA+ZczEXq4Ol9cSZ5C8Nd/HpvUbxxBX6sVgbtxS7KG4MhnPa7c3cUCTZOsi+rSPmYkbdtxTqxNm+pLX1Y0rytoDc2ycEJdA5jKDaORxxPiELrVb7narbiaePIVPEOjKCDfI5tNS+BJxgEq+GtbtHxx3rI8Jw6/GYv3JYqVRNkqI8mR2e5+BU5DkHJoOISlHGO4HnV3m9Pj6XNWXwkWT5TEPJxxnZJfn7RfQpKMJS7WrvzDuyUWgdtS0zpuZuYzPHmVEJeWrTf/cWU7Wjt1NeaC1VGgpEIbDF7GosMX9OrnsFZp2Z10CeC9I8rAj+AbR7YMpbSRn+tGuSuuC7FeEtfXTUiMBGAV/45VldAt5WFOD6H/Uavc0KziV8qG8KkNA7FBTOgZ8mDMcQfE0zKrQCb94/z8LBX+tIfOzXIQIi5HREFXT0EWFkdUhaoBJ/++JbLZsYk8r8A6LgLgmXQ3Wz39nJVwuvwhw0/wzdcje1VEvlNfRRE5zBB8phmRqNCN6TenXxVaKmYh/qAdmKncadTi3NVin+R7PdfixctFceukw8iG6Gr3610jvVZBK/cGWP/D8COJUQB0uXBjFKhF6VEoYx73zaB2QGrmU2HUs5DZa/AfQjEGo=</t>
   </si>
@@ -129,33 +138,31 @@
   </si>
   <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
-  </si>
-  <si>
-    <t>Denfensa Lateral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -166,38 +173,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -205,7 +217,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -395,26 +407,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -423,21 +438,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -484,12 +500,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B2" s="2">
-        <v>77.533</v>
+        <v>77.533000000000001</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -498,42 +514,42 @@
         <v>19</v>
       </c>
       <c r="E2" s="2">
-        <v>4.034</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="F2" s="2">
-        <v>0.303</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="K2" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2">
-        <v>4.957</v>
+        <v>4.9569999999999999</v>
       </c>
       <c r="M2" s="2">
         <v>-6.01</v>
       </c>
       <c r="N2" s="2">
-        <v>24.847</v>
+        <v>24.847000000000001</v>
       </c>
       <c r="O2" s="2">
-        <v>554.308</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>554.30799999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B3" s="2">
         <v>78.25</v>
@@ -545,45 +561,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>4.338</v>
+        <v>4.3380000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>0.344</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="G3" s="2">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="L3" s="2">
-        <v>5.078</v>
+        <v>5.0780000000000003</v>
       </c>
       <c r="M3" s="2">
-        <v>-5.857</v>
+        <v>-5.8570000000000002</v>
       </c>
       <c r="N3" s="2">
-        <v>26.993</v>
+        <v>26.992999999999999</v>
       </c>
       <c r="O3" s="2">
-        <v>881.296</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>881.29600000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B4" s="2">
-        <v>82.117</v>
+        <v>82.117000000000004</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -592,7 +608,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="2">
-        <v>4.567</v>
+        <v>4.5670000000000002</v>
       </c>
       <c r="F4" s="2">
         <v>0.318</v>
@@ -601,33 +617,33 @@
         <v>0.03</v>
       </c>
       <c r="H4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L4" s="2">
-        <v>4.626</v>
+        <v>4.6260000000000003</v>
       </c>
       <c r="M4" s="2">
-        <v>-5.738</v>
+        <v>-5.7380000000000004</v>
       </c>
       <c r="N4" s="2">
         <v>27.238</v>
       </c>
       <c r="O4" s="2">
-        <v>689.483</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>689.48299999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B5" s="2">
         <v>78.7</v>
@@ -639,42 +655,42 @@
         <v>21</v>
       </c>
       <c r="E5" s="2">
-        <v>4.675</v>
+        <v>4.6749999999999998</v>
       </c>
       <c r="F5" s="2">
-        <v>0.364</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="H5" s="2">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="I5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L5" s="2">
-        <v>5.297</v>
+        <v>5.2969999999999997</v>
       </c>
       <c r="M5" s="2">
         <v>-5.173</v>
       </c>
       <c r="N5" s="2">
-        <v>28.825</v>
+        <v>28.824999999999999</v>
       </c>
       <c r="O5" s="2">
         <v>758.1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B6" s="2">
         <v>82.75</v>
@@ -686,45 +702,45 @@
         <v>26</v>
       </c>
       <c r="E6" s="2">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="F6" s="2">
-        <v>0.278</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="G6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="K6" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="L6" s="2">
         <v>4.782</v>
       </c>
       <c r="M6" s="2">
-        <v>-4.788</v>
+        <v>-4.7880000000000003</v>
       </c>
       <c r="N6" s="2">
-        <v>24.235</v>
+        <v>24.234999999999999</v>
       </c>
       <c r="O6" s="2">
-        <v>751.556</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>751.55600000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B7" s="2">
-        <v>79.233</v>
+        <v>79.233000000000004</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -733,42 +749,42 @@
         <v>21</v>
       </c>
       <c r="E7" s="2">
-        <v>4.171</v>
+        <v>4.1710000000000003</v>
       </c>
       <c r="F7" s="2">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="L7" s="2">
-        <v>4.797</v>
+        <v>4.7969999999999997</v>
       </c>
       <c r="M7" s="2">
         <v>-4.694</v>
       </c>
       <c r="N7" s="2">
-        <v>27.281</v>
+        <v>27.280999999999999</v>
       </c>
       <c r="O7" s="2">
-        <v>761.347</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>761.34699999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B8" s="2">
         <v>77.55</v>
@@ -780,45 +796,45 @@
         <v>23</v>
       </c>
       <c r="E8" s="2">
-        <v>3.708</v>
+        <v>3.7080000000000002</v>
       </c>
       <c r="F8" s="2">
         <v>0.312</v>
       </c>
       <c r="G8" s="2">
-        <v>0.029</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K8" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2">
-        <v>5.433</v>
+        <v>5.4329999999999998</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.652</v>
+        <v>-5.6520000000000001</v>
       </c>
       <c r="N8" s="2">
         <v>28.134</v>
       </c>
       <c r="O8" s="2">
-        <v>543.669</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>543.66899999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B9" s="2">
-        <v>76.4</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -827,45 +843,45 @@
         <v>30</v>
       </c>
       <c r="E9" s="2">
-        <v>4.273</v>
+        <v>4.2729999999999997</v>
       </c>
       <c r="F9" s="2">
         <v>0.41</v>
       </c>
       <c r="G9" s="2">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="H9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J9" s="2">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="K9" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L9" s="2">
         <v>4.992</v>
       </c>
       <c r="M9" s="2">
-        <v>-5.239</v>
+        <v>-5.2389999999999999</v>
       </c>
       <c r="N9" s="2">
-        <v>27.839</v>
+        <v>27.838999999999999</v>
       </c>
       <c r="O9" s="2">
-        <v>729.739</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>729.73900000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B10" s="2">
-        <v>79.017</v>
+        <v>79.016999999999996</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -874,25 +890,25 @@
         <v>23</v>
       </c>
       <c r="E10" s="2">
-        <v>4.021</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="F10" s="2">
-        <v>0.368</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>0.031</v>
+        <v>3.1E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L10" s="2">
         <v>5.27</v>
@@ -901,15 +917,15 @@
         <v>-4.593</v>
       </c>
       <c r="N10" s="2">
-        <v>27.763</v>
+        <v>27.763000000000002</v>
       </c>
       <c r="O10" s="2">
-        <v>780.339</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>780.33900000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B11" s="2">
         <v>83.9</v>
@@ -921,45 +937,45 @@
         <v>30</v>
       </c>
       <c r="E11" s="2">
-        <v>4.629</v>
+        <v>4.6289999999999996</v>
       </c>
       <c r="F11" s="2">
-        <v>0.347</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="G11" s="2">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K11" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L11" s="2">
-        <v>4.449</v>
+        <v>4.4489999999999998</v>
       </c>
       <c r="M11" s="2">
-        <v>-6.091</v>
+        <v>-6.0910000000000002</v>
       </c>
       <c r="N11" s="2">
-        <v>28.188</v>
+        <v>28.187999999999999</v>
       </c>
       <c r="O11" s="2">
-        <v>235.514</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>235.51400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B12" s="2">
-        <v>79.183</v>
+        <v>79.183000000000007</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -968,7 +984,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="2">
-        <v>4.053</v>
+        <v>4.0529999999999999</v>
       </c>
       <c r="F12" s="2">
         <v>0.36</v>
@@ -977,36 +993,36 @@
         <v>0.06</v>
       </c>
       <c r="H12" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K12" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="L12" s="2">
-        <v>5.389</v>
+        <v>5.3890000000000002</v>
       </c>
       <c r="M12" s="2">
-        <v>-4.797</v>
+        <v>-4.7969999999999997</v>
       </c>
       <c r="N12" s="2">
         <v>27.968</v>
       </c>
       <c r="O12" s="2">
-        <v>693.647</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>693.64700000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B13" s="2">
-        <v>77.333</v>
+        <v>77.332999999999998</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -1018,42 +1034,42 @@
         <v>4.375</v>
       </c>
       <c r="F13" s="2">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="G13" s="2">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="K13" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L13" s="2">
         <v>5.33</v>
       </c>
       <c r="M13" s="2">
-        <v>-4.403</v>
+        <v>-4.4029999999999996</v>
       </c>
       <c r="N13" s="2">
-        <v>26.914</v>
+        <v>26.914000000000001</v>
       </c>
       <c r="O13" s="2">
         <v>920.452</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B14" s="2">
-        <v>75.783</v>
+        <v>75.783000000000001</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>36</v>
@@ -1062,42 +1078,42 @@
         <v>34</v>
       </c>
       <c r="E14" s="2">
-        <v>4.064</v>
+        <v>4.0640000000000001</v>
       </c>
       <c r="F14" s="2">
-        <v>0.296</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="G14" s="2">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
       <c r="H14" s="2">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I14" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K14" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="L14" s="2">
         <v>4.92</v>
       </c>
       <c r="M14" s="2">
-        <v>-4.957</v>
+        <v>-4.9569999999999999</v>
       </c>
       <c r="N14" s="2">
-        <v>29.696</v>
+        <v>29.696000000000002</v>
       </c>
       <c r="O14" s="2">
-        <v>790.512</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>790.51199999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B15" s="2">
         <v>82.9</v>
@@ -1112,39 +1128,39 @@
         <v>4.47</v>
       </c>
       <c r="F15" s="2">
-        <v>0.464</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="G15" s="2">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H15" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="K15" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L15" s="2">
-        <v>5.211</v>
+        <v>5.2110000000000003</v>
       </c>
       <c r="M15" s="2">
         <v>-6.048</v>
       </c>
       <c r="N15" s="2">
-        <v>26.399</v>
+        <v>26.399000000000001</v>
       </c>
       <c r="O15" s="2">
         <v>183.39</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="B16" s="2">
         <v>78.95</v>
@@ -1153,34 +1169,34 @@
         <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2">
-        <v>4.028</v>
+        <v>4.0279999999999996</v>
       </c>
       <c r="F16" s="2">
-        <v>0.329</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="G16" s="2">
-        <v>0.032</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H16" s="2">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I16" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="K16" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L16" s="2">
-        <v>5.743</v>
+        <v>5.7430000000000003</v>
       </c>
       <c r="M16" s="2">
-        <v>-6.021</v>
+        <v>-6.0209999999999999</v>
       </c>
       <c r="N16" s="2">
         <v>31.709</v>
@@ -1190,6 +1206,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>